--- a/task-reviews/icons/task_icons_counting_size_relation/task_icons_counting_size_relation.xlsx
+++ b/task-reviews/icons/task_icons_counting_size_relation/task_icons_counting_size_relation.xlsx
@@ -155,9 +155,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -183,9 +180,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -211,9 +205,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -239,9 +230,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -267,9 +255,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -295,9 +280,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -323,9 +305,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -351,9 +330,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -379,9 +355,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -407,9 +380,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -435,9 +405,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -463,9 +430,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -491,9 +455,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -519,9 +480,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -547,9 +505,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -575,9 +530,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -603,9 +555,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -631,9 +580,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -659,9 +605,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -687,9 +630,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -715,9 +655,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -743,9 +680,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -771,9 +705,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -799,9 +730,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -827,9 +755,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -855,9 +780,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -883,9 +805,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -911,9 +830,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -939,9 +855,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -967,9 +880,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -995,9 +905,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1023,9 +930,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1051,9 +955,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1079,9 +980,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1107,9 +1005,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1135,9 +1030,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1163,9 +1055,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1191,9 +1080,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1219,9 +1105,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1247,9 +1130,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1275,9 +1155,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1303,9 +1180,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1331,9 +1205,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1359,9 +1230,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1387,9 +1255,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1415,9 +1280,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1443,9 +1305,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1471,9 +1330,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1499,9 +1355,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1527,9 +1380,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1560,9 +1410,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1588,9 +1435,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1616,9 +1460,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1644,9 +1485,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1672,9 +1510,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1700,9 +1535,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1728,9 +1560,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1756,9 +1585,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1784,9 +1610,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1812,9 +1635,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1840,9 +1660,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1868,9 +1685,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1896,9 +1710,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1924,9 +1735,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1952,9 +1760,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1980,9 +1785,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2008,9 +1810,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2036,9 +1835,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2064,9 +1860,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2092,9 +1885,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2120,9 +1910,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2148,9 +1935,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2176,9 +1960,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2204,9 +1985,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2232,9 +2010,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2260,9 +2035,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2288,9 +2060,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2316,9 +2085,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2344,9 +2110,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2372,9 +2135,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2400,9 +2160,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2428,9 +2185,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2456,9 +2210,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2484,9 +2235,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2512,9 +2260,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2540,9 +2285,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2568,9 +2310,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2596,9 +2335,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2624,9 +2360,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2652,9 +2385,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2680,9 +2410,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2708,9 +2435,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2736,9 +2460,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2764,9 +2485,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2792,9 +2510,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2820,9 +2535,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2848,9 +2560,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2876,9 +2585,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2904,9 +2610,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2932,9 +2635,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
